--- a/artfynd/A 3658-2024 artfynd.xlsx
+++ b/artfynd/A 3658-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3658-2024 artfynd.xlsx
+++ b/artfynd/A 3658-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114846388</v>
+        <v>114846690</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572442</v>
+        <v>572538</v>
       </c>
       <c r="R2" t="n">
-        <v>6405879</v>
+        <v>6405826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,47 +784,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114846413</v>
+        <v>114846728</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572451</v>
+        <v>572548</v>
       </c>
       <c r="R3" t="n">
-        <v>6405855</v>
+        <v>6405832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,47 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114846189</v>
+        <v>114846874</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572366</v>
+        <v>572566</v>
       </c>
       <c r="R4" t="n">
-        <v>6405905</v>
+        <v>6405742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,47 +1002,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114846590</v>
+        <v>114846905</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572478</v>
+        <v>572500</v>
       </c>
       <c r="R5" t="n">
-        <v>6405865</v>
+        <v>6405769</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114846652</v>
+        <v>114846189</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572491</v>
+        <v>572366</v>
       </c>
       <c r="R6" t="n">
-        <v>6405837</v>
+        <v>6405905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,50 +1217,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114846905</v>
+        <v>114846214</v>
       </c>
       <c r="B7" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572500</v>
+        <v>572358</v>
       </c>
       <c r="R7" t="n">
-        <v>6405769</v>
+        <v>6405902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,50 +1327,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114846874</v>
+        <v>114846388</v>
       </c>
       <c r="B8" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572566</v>
+        <v>572442</v>
       </c>
       <c r="R8" t="n">
-        <v>6405742</v>
+        <v>6405879</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,15 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114846214</v>
+        <v>114846413</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,11 +1461,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1510,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572358</v>
+        <v>572451</v>
       </c>
       <c r="R9" t="n">
-        <v>6405902</v>
+        <v>6405855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,15 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114846540</v>
+        <v>114846436</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572473</v>
+        <v>572458</v>
       </c>
       <c r="R10" t="n">
-        <v>6405873</v>
+        <v>6405869</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,15 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114846670</v>
+        <v>114846513</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572504</v>
+        <v>572466</v>
       </c>
       <c r="R11" t="n">
-        <v>6405820</v>
+        <v>6405883</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,15 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114846630</v>
+        <v>114846540</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572488</v>
+        <v>572473</v>
       </c>
       <c r="R12" t="n">
-        <v>6405837</v>
+        <v>6405873</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,15 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114846513</v>
+        <v>114846561</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572466</v>
+        <v>572483</v>
       </c>
       <c r="R13" t="n">
-        <v>6405883</v>
+        <v>6405870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,15 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114846436</v>
+        <v>114846590</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572458</v>
+        <v>572478</v>
       </c>
       <c r="R14" t="n">
-        <v>6405869</v>
+        <v>6405865</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,6 +2066,324 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114846630</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 3658, Dövestad, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572488</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6405837</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114846652</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 3658, Dövestad, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572491</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6405837</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114846670</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 3658, Dövestad, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>572504</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6405820</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
